--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T13:35:06+00:00</t>
+    <t>2026-08-04T12:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/organization-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -741,7 +741,7 @@
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Organization business identifier</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -837,7 +837,7 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>Name used for the organization</t>
+    <t>Name of the organization</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
@@ -881,7 +881,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
+    <t>Organization telecom</t>
   </si>
   <si>
     <t>A contact detail for the organization.</t>
@@ -953,7 +953,7 @@
 </t>
   </si>
   <si>
-    <t>The organization of which this organization forms a part</t>
+    <t>The organization of which this organization is part of: e.g. an ERN</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -1049,7 +1049,7 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
+    <t>Organization contact infos</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
